--- a/請求書雛形.xlsx
+++ b/請求書雛形.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/notsuou/Desktop/アドビ関係/1.1.0.Adobe関係→クライアント/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/notsuou/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD9EDCD-E476-1B41-AC50-BA315DBE2268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF632598-D4FB-D244-BABE-07B45270630A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="980" windowWidth="28860" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15760" yWindow="780" windowWidth="28860" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>詳細</t>
   </si>
@@ -95,23 +95,6 @@
     <phoneticPr fontId="17"/>
   </si>
   <si>
-    <t>請求日：2025/09/30</t>
-    <rPh sb="0" eb="3">
-      <t>セイキュウ</t>
-    </rPh>
-    <phoneticPr fontId="17"/>
-  </si>
-  <si>
-    <t>支払い期日：2025/10/31</t>
-    <rPh sb="0" eb="2">
-      <t>シハライ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キジテゥ</t>
-    </rPh>
-    <phoneticPr fontId="17"/>
-  </si>
-  <si>
     <t>野津　欧　</t>
     <rPh sb="0" eb="2">
       <t>ノテゥ</t>
@@ -122,14 +105,52 @@
     <phoneticPr fontId="17"/>
   </si>
   <si>
-    <t>　　　様</t>
-    <rPh sb="3" eb="4">
-      <t>サマ</t>
+    <t>山口雄貴様</t>
+  </si>
+  <si>
+    <t>請求日：2026/08/05</t>
+    <rPh sb="0" eb="3">
+      <t>セイキュウ</t>
     </rPh>
     <phoneticPr fontId="17"/>
   </si>
   <si>
-    <t>請求書 No.</t>
+    <t>支払い期日：2026/08/31</t>
+    <rPh sb="0" eb="2">
+      <t>シハライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キジテゥ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>7本分_7月分（通常動画7点・オンラインサロン分は8月に振替）</t>
+    <rPh sb="1" eb="3">
+      <t>ホn</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガテゥ</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>テn</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ブn</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ガテゥ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フリカエ</t>
+    </rPh>
+    <phoneticPr fontId="17"/>
+  </si>
+  <si>
+    <t>請求書 No.202</t>
     <phoneticPr fontId="17"/>
   </si>
 </sst>
@@ -146,7 +167,7 @@
     <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="179" formatCode="[&lt;=99999999]####\-####;\(00\)\ ####\-####"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="4"/>
@@ -285,13 +306,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="29"/>
-      <color theme="5"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="4"/>
@@ -317,6 +331,13 @@
       <sz val="16"/>
       <color theme="5"/>
       <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FFB07C1A"/>
+      <name val="メイリオ"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
@@ -667,7 +688,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -677,23 +698,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="179" fontId="18" fillId="0" borderId="0" xfId="11" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="7" fontId="18" fillId="2" borderId="0" xfId="8" applyFont="1" applyBorder="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="178" fontId="22" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="18" fillId="2" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
@@ -709,9 +729,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="9" applyFont="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="20% - アクセント 1" xfId="27" builtinId="30" customBuiltin="1"/>
@@ -1186,7 +1210,7 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:C26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="46.28515625" style="2" customWidth="1"/>
@@ -1195,141 +1219,148 @@
     <col min="5" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:3" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="2:3" ht="50" customHeight="1">
+      <c r="B2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="2:3" ht="23" customHeight="1">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="2:3" ht="16"/>
+    <row r="5" spans="2:3" ht="18" customHeight="1"/>
+    <row r="6" spans="2:3" ht="22">
+      <c r="B6" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="19" customHeight="1">
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="30" customHeight="1">
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="17">
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="16">
+      <c r="C10" s="14"/>
+    </row>
+    <row r="11" spans="2:3" ht="16">
+      <c r="B11" s="3"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="2:3" ht="30" customHeight="1">
+      <c r="B12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="30" customHeight="1">
+      <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="2:3" ht="50" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-    </row>
-    <row r="4" spans="2:3" ht="16" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="C10" s="15"/>
-    </row>
-    <row r="11" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="4"/>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="14"/>
-    </row>
-    <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="14"/>
-    </row>
-    <row r="15" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="14"/>
-    </row>
-    <row r="16" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="13">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="30" customHeight="1">
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15" spans="2:3" ht="30" customHeight="1">
+      <c r="C15" s="13"/>
+    </row>
+    <row r="16" spans="2:3" ht="30" customHeight="1">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="2:3" ht="30" customHeight="1">
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="2:3" ht="30" customHeight="1">
       <c r="B18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="9" t="s">
+    <row r="19" spans="2:3" ht="30" customHeight="1">
+      <c r="B19" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="12">
         <f>IFERROR(SUM(InvoiceDetails[金額]), "")</f>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="30" customHeight="1">
+      <c r="B20" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="12">
+    <row r="21" spans="2:3" ht="30" customHeight="1">
+      <c r="B21" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="2:3" ht="30" customHeight="1">
+      <c r="B22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="12">
         <f>IFERROR(C19*(1+C20)+C21, "")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="16" t="s">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="30" customHeight="1">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+    </row>
+    <row r="24" spans="2:3" ht="30" customHeight="1">
+      <c r="B24" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="C24" s="15"/>
+    </row>
+    <row r="25" spans="2:3" ht="30" customHeight="1">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+    </row>
+    <row r="26" spans="2:3" ht="30" customHeight="1">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B2:C2"/>
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>

--- a/請求書雛形.xlsx
+++ b/請求書雛形.xlsx
@@ -160,10 +160,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="7">
     <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
-    <numFmt numFmtId="7" formatCode="&quot;¥&quot;#,##0.00;&quot;¥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="7" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="179" formatCode="[&lt;=99999999]####\-####;\(00\)\ ####\-####"/>
   </numFmts>
@@ -704,7 +704,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="7" fontId="18" fillId="2" borderId="0" xfId="8" applyFont="1" applyBorder="1">
+    <xf applyNumberFormat="1" numFmtId="5" fontId="18" fillId="2" borderId="0" xfId="8" applyFont="1" applyBorder="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1">
@@ -808,7 +808,7 @@
         <charset val="128"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="11" formatCode="&quot;¥&quot;#,##0.00;&quot;¥&quot;\-#,##0.00"/>
+      <numFmt numFmtId="11" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
     </dxf>
     <dxf>
       <font>
